--- a/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_tier.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/sensibilidade_tier.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -421,13 +421,13 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.04486941313379269</v>
+        <v>0.06290875280931077</v>
       </c>
       <c r="E3">
-        <v>0.05538273110889344</v>
+        <v>0.1066540142239678</v>
       </c>
       <c r="F3">
-        <v>1.056877708521618</v>
+        <v>4.471619146413766</v>
       </c>
     </row>
     <row r="4">
@@ -443,13 +443,13 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>0.0715760285814679</v>
+        <v>0.007406380896008698</v>
       </c>
       <c r="E4">
-        <v>0.2401404624100854</v>
+        <v>0.1000699399382928</v>
       </c>
       <c r="F4">
-        <v>18.36044885566818</v>
+        <v>9.709256629607541</v>
       </c>
     </row>
     <row r="5">
@@ -462,16 +462,16 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>0.007406380896008698</v>
+        <v>-0.2787298060244909</v>
       </c>
       <c r="E5">
-        <v>0.1000699399382928</v>
+        <v>0.4193334963587222</v>
       </c>
       <c r="F5">
-        <v>9.709256629607541</v>
+        <v>100.9856451553733</v>
       </c>
     </row>
     <row r="6">
@@ -487,13 +487,13 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>-0.2787298060244909</v>
+        <v>0.1716000227658836</v>
       </c>
       <c r="E6">
-        <v>0.4193334963587222</v>
+        <v>0.555779164827344</v>
       </c>
       <c r="F6">
-        <v>100.9856451553733</v>
+        <v>46.84084718421151</v>
       </c>
     </row>
     <row r="7">
@@ -503,19 +503,36 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0.1716000227658836</v>
-      </c>
-      <c r="E7">
-        <v>0.555779164827344</v>
-      </c>
-      <c r="F7">
-        <v>46.84084718421151</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
